--- a/artfynd/A 27617-2020 artfynd.xlsx
+++ b/artfynd/A 27617-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27617-2020 artfynd.xlsx
+++ b/artfynd/A 27617-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3842996</v>
+        <v>62343985</v>
       </c>
       <c r="B2" t="n">
         <v>103427</v>
@@ -705,19 +705,26 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Persbo, numera obebodd gård, Hls</t>
+          <t>Persbo, numera övergiven gård, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573289.2670216083</v>
+        <v>573288.7922707899</v>
       </c>
       <c r="R2" t="n">
-        <v>6770814.386630494</v>
+        <v>6770813.892544731</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -739,14 +746,9 @@
           <t>Hanebo</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>XH-Bol-0022</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-07-14</t>
+          <t>2016-08-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -756,7 +758,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-07-14</t>
+          <t>2016-08-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -764,35 +766,41 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kobete, påsläpp i maj, tidigblommande</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>stor inhägnad naturbetesmark, delvis gödselpåverkad</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Delin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62343985</v>
+        <v>82703703</v>
       </c>
       <c r="B3" t="n">
         <v>103427</v>
@@ -822,26 +830,19 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Persbo, numera övergiven gård, Hls</t>
+          <t>Persbo, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573288.7922707899</v>
+        <v>573279.2771465223</v>
       </c>
       <c r="R3" t="n">
-        <v>6770813.892544731</v>
+        <v>6770804.978888964</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,9 +864,14 @@
           <t>Hanebo</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>DIN198607141320</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-04</t>
+          <t>1986-07-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -875,7 +881,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-04</t>
+          <t>1986-07-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -883,13 +889,8 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kobete, påsläpp i maj, tidigblommande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -899,28 +900,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>stor inhägnad naturbetesmark, delvis gödselpåverkad</t>
+          <t>Ålderdomligt jordbruk vägkant äng åkerkant gödselstack</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Björn Wannberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82703703</v>
+        <v>110766349</v>
       </c>
       <c r="B4" t="n">
-        <v>103427</v>
+        <v>103450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,20 +951,36 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Persbo, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573279.2771465223</v>
+        <v>573366.1611080903</v>
       </c>
       <c r="R4" t="n">
-        <v>6770804.978888964</v>
+        <v>6770754.968262777</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,14 +1002,9 @@
           <t>Hanebo</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>DIN198607141320</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1986-07-14</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -998,7 +1014,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1986-07-14</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1006,43 +1022,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer i torrbacken nedom den östra tallen, ovanpå och i slänten av en liten kulle. Endast torra fröställningar (några med frö) kunde återfinnas trots noggrannt letande.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Ålderdomligt jordbruk vägkant äng åkerkant gödselstack</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Delin</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
+          <t>Gustav Wikström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110766349</v>
+        <v>111638744</v>
       </c>
       <c r="B5" t="n">
-        <v>103450</v>
+        <v>103451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,22 +1068,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221447</v>
+        <v>698</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
+          <t>Gentianella campestris var. campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1080,7 +1093,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1091,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573366.1611080903</v>
+        <v>573378</v>
       </c>
       <c r="R5" t="n">
-        <v>6770754.968262777</v>
+        <v>6770759</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,27 +1134,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer i torrbacken nedom den östra tallen, ovanpå och i slänten av en liten kulle. Endast torra fröställningar (några med frö) kunde återfinnas trots noggrannt letande.</t>
+          <t>Växer i närheten av de två tallarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,22 +1160,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Jan Moberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Jan Moberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110767291</v>
+        <v>112726482</v>
       </c>
       <c r="B6" t="n">
-        <v>104556</v>
+        <v>86664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,49 +1184,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221447</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Persbo, numera obebodd gård, Hls</t>
+          <t>Persbo, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573289</v>
+        <v>573369</v>
       </c>
       <c r="R6" t="n">
-        <v>6770814</v>
+        <v>6770750</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,24 +1247,14 @@
           <t>Hanebo</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>XH-Bol-0022</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återupptäckt av Stefan Olander 6 juli 2022 (dock inte rapporterad på AP). Fältgentianan vid Persbo omnämns i VäX 2022 nr 2. Fältgentianan växer nedom den östra av två tallar öster om vägen (koord. N 6770756, E 573368) som går upp till den obebodda gården. Det fanns 42 helt torra fröställningar, varav några med frö, vid denna plats. Det är möjligt att fältgentianan blommar mycket tidigt här varav tidigare besök kanske krävs. Darrgräs växer även här. Enligt samtal med Stefan ska det även växa fältgentian vid en liten kulle närmare den gamla nedgångna rundtimmerladan väster om vägen men denna växtplats kunde inte hittas.</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,29 +1267,35 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Stefan Olander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige, Fältgentiana X-län</t>
-        </is>
-      </c>
+          <t>Stefan Olander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111638744</v>
+        <v>112726432</v>
       </c>
       <c r="B7" t="n">
-        <v>103451</v>
+        <v>86641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,39 +1304,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>698</v>
+        <v>4377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sen fältgentiana</t>
+          <t>Blodvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. campestris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573378</v>
+        <v>573369</v>
       </c>
       <c r="R7" t="n">
-        <v>6770759</v>
+        <v>6770750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,17 +1369,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer i närheten av de två tallarna.</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,25 +1387,35 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Moberg</t>
+          <t>Stefan Olander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Moberg</t>
+          <t>Stefan Olander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112726482</v>
+        <v>112726381</v>
       </c>
       <c r="B8" t="n">
-        <v>86664</v>
+        <v>86821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,27 +1424,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>805</v>
+        <v>4392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>3</t>
@@ -1531,242 +1525,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112726432</v>
-      </c>
-      <c r="B9" t="n">
-        <v>86641</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4377</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Blodvaxskivling</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hygrocybe coccinea</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Persbo, Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>573369</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6770750</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Hanebo</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Naturbetesmark.</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Stefan Olander</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Stefan Olander</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112726381</v>
-      </c>
-      <c r="B10" t="n">
-        <v>86821</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4392</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ängsvaxskivling</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Persbo, Hls</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>573369</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6770750</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Hanebo</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Naturbetesmark.</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Stefan Olander</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Stefan Olander</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
